--- a/data/publications.xlsx
+++ b/data/publications.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SmartCity20\.gemini\antigravity\scratch\surd-lab-homepage\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{686A9505-5DA0-494C-BC72-76650D6F07B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EB47416-67D1-4DB5-ACE8-F5ACAF9990ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25800" yWindow="0" windowWidth="25800" windowHeight="21000" xr2:uid="{FB3B5A28-B30A-4FB9-B973-DA7691D44842}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25800" windowHeight="21000" xr2:uid="{FB3B5A28-B30A-4FB9-B973-DA7691D44842}"/>
   </bookViews>
   <sheets>
     <sheet name="publications" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1410" uniqueCount="604">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1430" uniqueCount="614">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2186,6 +2186,43 @@
   <si>
     <t>type_index</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PUB-135</t>
+  </si>
+  <si>
+    <t>류준영, 남진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업단지 재생을 위한 공공투자 거버넌스 효율화 방안 연구: 한국과 일본의 운용 모델 비교를 중심으로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>223-346</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026, 류준영, 남진, 산업단지 재생을 위한 공공투자 거버넌스 효율화 방안 연구 _ 한국과 일본의 운용 모델 비교를 중심으로, 도시부동산연구, 17(1), 223-246</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PUB-136</t>
+  </si>
+  <si>
+    <t>이채은, 남진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울시 청년안심주택 입지 유형화 및 특성 분석에 관한 연구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>95-119</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026, 이채은, 남진, 서울시 청년안심주택 입지 유형화 및 특성 분석에 관한 연구, 도시부동산연구, 17(2), 95-119</t>
   </si>
 </sst>
 </file>
@@ -2241,7 +2278,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2252,6 +2289,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2292,8 +2332,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3B219D66-BA1A-4F2C-94F2-DC6495E11B62}" name="PublicationsTable" displayName="PublicationsTable" ref="A1:Q135" totalsRowShown="0">
-  <autoFilter ref="A1:Q135" xr:uid="{3B219D66-BA1A-4F2C-94F2-DC6495E11B62}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3B219D66-BA1A-4F2C-94F2-DC6495E11B62}" name="PublicationsTable" displayName="PublicationsTable" ref="A1:Q137" totalsRowShown="0">
+  <autoFilter ref="A1:Q137" xr:uid="{3B219D66-BA1A-4F2C-94F2-DC6495E11B62}"/>
   <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{A3F79930-0951-4BB1-9334-E9583C167FB9}" name="id"/>
     <tableColumn id="2" xr3:uid="{E3831AFD-57F7-42F7-9B92-611D56962AE7}" name="type"/>
@@ -2646,7 +2686,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDD90BD3-3697-404D-A251-253A8639131A}">
-  <dimension ref="A1:Q135"/>
+  <dimension ref="A1:Q137"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="12.125" customWidth="1"/>
@@ -8014,16 +8054,100 @@
         <v>287</v>
       </c>
     </row>
+    <row r="136" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>604</v>
+      </c>
+      <c r="B136" t="s">
+        <v>285</v>
+      </c>
+      <c r="C136" t="s">
+        <v>600</v>
+      </c>
+      <c r="D136">
+        <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
+        <v>2026</v>
+      </c>
+      <c r="E136" t="s">
+        <v>605</v>
+      </c>
+      <c r="F136" t="s">
+        <v>606</v>
+      </c>
+      <c r="G136" t="s">
+        <v>533</v>
+      </c>
+      <c r="H136">
+        <v>17</v>
+      </c>
+      <c r="I136">
+        <v>1</v>
+      </c>
+      <c r="J136" t="s">
+        <v>607</v>
+      </c>
+      <c r="M136" t="s">
+        <v>434</v>
+      </c>
+      <c r="O136" s="4" t="s">
+        <v>608</v>
+      </c>
+      <c r="P136" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="137" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>609</v>
+      </c>
+      <c r="B137" t="s">
+        <v>285</v>
+      </c>
+      <c r="C137" t="s">
+        <v>600</v>
+      </c>
+      <c r="D137">
+        <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
+        <v>2026</v>
+      </c>
+      <c r="E137" t="s">
+        <v>610</v>
+      </c>
+      <c r="F137" t="s">
+        <v>611</v>
+      </c>
+      <c r="G137" t="s">
+        <v>533</v>
+      </c>
+      <c r="H137">
+        <v>17</v>
+      </c>
+      <c r="I137">
+        <v>2</v>
+      </c>
+      <c r="J137" t="s">
+        <v>612</v>
+      </c>
+      <c r="M137" t="s">
+        <v>434</v>
+      </c>
+      <c r="O137" s="4" t="s">
+        <v>613</v>
+      </c>
+      <c r="P137" t="s">
+        <v>287</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B135" xr:uid="{4097AEAF-A1C2-4390-9B06-0AF57FD443A1}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B137" xr:uid="{4097AEAF-A1C2-4390-9B06-0AF57FD443A1}">
       <formula1>"Journal,Conference,Book,Report"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C135" xr:uid="{DF9A1197-E5D4-4C18-8B8C-E3B493C707CA}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C137" xr:uid="{DF9A1197-E5D4-4C18-8B8C-E3B493C707CA}">
       <formula1>"SSCI,SCIE,KCI,Other,Unverified,Not applicable"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P135 M2:M135" xr:uid="{24D29147-F31F-48DB-8F1C-55C5A592175F}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P137 M2:M137" xr:uid="{24D29147-F31F-48DB-8F1C-55C5A592175F}">
       <formula1>"Y,N"</formula1>
     </dataValidation>
   </dataValidations>

--- a/data/publications.xlsx
+++ b/data/publications.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SmartCity20\.gemini\antigravity\scratch\surd-lab-homepage\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EB47416-67D1-4DB5-ACE8-F5ACAF9990ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B00B015-CD3E-42A6-8685-316E8652F85A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25800" windowHeight="21000" xr2:uid="{FB3B5A28-B30A-4FB9-B973-DA7691D44842}"/>
+    <workbookView xWindow="25800" yWindow="0" windowWidth="25800" windowHeight="21000" xr2:uid="{FB3B5A28-B30A-4FB9-B973-DA7691D44842}"/>
   </bookViews>
   <sheets>
     <sheet name="publications" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1430" uniqueCount="614">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1503" uniqueCount="686">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2223,6 +2223,233 @@
   </si>
   <si>
     <t>2026, 이채은, 남진, 서울시 청년안심주택 입지 유형화 및 특성 분석에 관한 연구, 도시부동산연구, 17(2), 95-119</t>
+  </si>
+  <si>
+    <t>https://www.dbpia.co.kr/journal/articleDetail?nodeId=NODE00780284</t>
+  </si>
+  <si>
+    <t>https://www.dbpia.co.kr/journal/articleDetail?nodeId=NODE01015110</t>
+  </si>
+  <si>
+    <t>https://www.dbpia.co.kr/journal/articleDetail?nodeId=NODE00788148</t>
+  </si>
+  <si>
+    <t>https://www.dbpia.co.kr/journal/articleDetail?nodeId=NODE01538231</t>
+  </si>
+  <si>
+    <t>https://www.dbpia.co.kr/journal/articleDetail?nodeId=NODE00787735</t>
+  </si>
+  <si>
+    <t>https://www.dbpia.co.kr/journal/articleDetail?nodeId=NODE01445265</t>
+  </si>
+  <si>
+    <t>https://www.dbpia.co.kr/journal/articleDetail?nodeId=NODE00774766</t>
+  </si>
+  <si>
+    <t>https://www.dbpia.co.kr/journal/articleDetail?nodeId=NODE01168221</t>
+  </si>
+  <si>
+    <t>https://www.dbpia.co.kr/journal/articleDetail?nodeId=NODE00786069</t>
+  </si>
+  <si>
+    <t>https://www.dbpia.co.kr/journal/articleDetail?nodeId=NODE00786282</t>
+  </si>
+  <si>
+    <t>https://www.dbpia.co.kr/journal/articleDetail?nodeId=NODE00787734</t>
+  </si>
+  <si>
+    <t>https://www.dbpia.co.kr/journal/articleDetail?nodeId=NODE00787661</t>
+  </si>
+  <si>
+    <t>https://www.dbpia.co.kr/journal/articleDetail?nodeId=NODE01169931</t>
+  </si>
+  <si>
+    <t>https://www.dbpia.co.kr/journal/articleDetail?nodeId=NODE00788035</t>
+  </si>
+  <si>
+    <t>https://www.dbpia.co.kr/journal/articleDetail?nodeId=NODE00798946</t>
+  </si>
+  <si>
+    <t>https://www.dbpia.co.kr/journal/articleDetail?nodeId=NODE00788149</t>
+  </si>
+  <si>
+    <t>https://www.dbpia.co.kr/journal/articleDetail?nodeId=NODE00853974</t>
+  </si>
+  <si>
+    <t>https://www.dbpia.co.kr/journal/articleDetail?nodeId=NODE00937692</t>
+  </si>
+  <si>
+    <t>https://www.dbpia.co.kr/journal/articleDetail?nodeId=NODE01015101</t>
+  </si>
+  <si>
+    <t>https://www.kci.go.kr/kciportal/ci/sereArticleSearch/ciSereArtiView.kci?sereArticleSearchBean.artiId=ART003226769</t>
+  </si>
+  <si>
+    <t>https://www.kci.go.kr/kciportal/ci/sereArticleSearch/ciSereArtiView.kci?sereArticleSearchBean.artiId=ART003295061</t>
+  </si>
+  <si>
+    <t>https://www.kci.go.kr/kciportal/ci/sereArticleSearch/ciSereArtiView.kci?sereArticleSearchBean.artiId=ART003194707</t>
+  </si>
+  <si>
+    <t>https://www.kci.go.kr/kciportal/ci/sereArticleSearch/ciSereArtiView.kci?sereArticleSearchBean.artiId=ART003215786</t>
+  </si>
+  <si>
+    <t>https://www.kci.go.kr/kciportal/ci/sereArticleSearch/ciSereArtiView.kci?sereArticleSearchBean.artiId=ART003295065</t>
+  </si>
+  <si>
+    <t>https://www.kci.go.kr/kciportal/ci/sereArticleSearch/ciSereArtiView.kci?sereArticleSearchBean.artiId=ART003255244</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.kci.go.kr/kciportal/ci/sereArticleSearch/ciSereArtiView.kci?sereArticleSearchBean.artiId=ART003128104</t>
+  </si>
+  <si>
+    <t>https://www.kci.go.kr/kciportal/ci/sereArticleSearch/ciSereArtiView.kci?sereArticleSearchBean.artiId=ART003142087</t>
+  </si>
+  <si>
+    <t>https://www.kci.go.kr/kciportal/ci/sereArticleSearch/ciSereArtiView.kci?sereArticleSearchBean.artiId=ART003102518</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/article/pii/S0264275124002609</t>
+  </si>
+  <si>
+    <t>https://www.kci.go.kr/kciportal/ci/sereArticleSearch/ciSereArtiView.kci?sereArticleSearchBean.artiId=ART003167791</t>
+  </si>
+  <si>
+    <t>https://www.kci.go.kr/kciportal/ci/sereArticleSearch/ciSereArtiView.kci?sereArticleSearchBean.artiId=ART003167787</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.kci.go.kr/kciportal/ci/sereArticleSearch/ciSereArtiView.kci?sereArticleSearchBean.artiId=ART002950680</t>
+  </si>
+  <si>
+    <t>https://www.kci.go.kr/kciportal/ci/sereArticleSearch/ciSereArtiView.kci?sereArticleSearchBean.artiId=ART002955955</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.kci.go.kr/kciportal/ci/sereArticleSearch/ciSereArtiView.kci?sereArticleSearchBean.artiId=ART002932199</t>
+  </si>
+  <si>
+    <t>https://www.kci.go.kr/kciportal/ci/sereArticleSearch/ciSereArtiView.kci?sereArticleSearchBean.artiId=ART002982365</t>
+  </si>
+  <si>
+    <t>https://www.kci.go.kr/kciportal/ci/sereArticleSearch/ciSereArtiView.kci?sereArticleSearchBean.artiId=ART002975694</t>
+  </si>
+  <si>
+    <t>https://www.dbpia.co.kr/journal/articleDetail?nodeId=NODE11509560</t>
+  </si>
+  <si>
+    <t>https://www.kci.go.kr/kciportal/ci/sereArticleSearch/ciSereArtiView.kci?sereArticleSearchBean.artiId=ART003045752</t>
+  </si>
+  <si>
+    <t>https://www.kci.go.kr/kciportal/ci/sereArticleSearch/ciSereArtiView.kci?sereArticleSearchBean.artiId=ART002831394</t>
+  </si>
+  <si>
+    <t>https://www.kci.go.kr/kciportal/ci/sereArticleSearch/ciSereArtiView.kci?sereArticleSearchBean.artiId=ART002887200</t>
+  </si>
+  <si>
+    <t>https://www.kci.go.kr/kciportal/ci/sereArticleSearch/ciSereArtiView.kci?sereArticleSearchBean.artiId=ART002815134</t>
+  </si>
+  <si>
+    <t>https://www.kci.go.kr/kciportal/ci/sereArticleSearch/ciSereArtiView.kci?sereArticleSearchBean.artiId=ART002826329</t>
+  </si>
+  <si>
+    <t>https://www.kci.go.kr/kciportal/ci/sereArticleSearch/ciSereArtiView.kci?sereArticleSearchBean.artiId=ART003023685</t>
+  </si>
+  <si>
+    <t>https://www.dbpia.co.kr/journal/articleDetail?nodeId=NODE11052514</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.dbpia.co.kr/journal/articleDetail?nodeId=NODE11124347</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.kci.go.kr/kciportal/ci/sereArticleSearch/ciSereArtiView.kci?sereArticleSearchBean.artiId=ART002925258</t>
+  </si>
+  <si>
+    <t>https://www.kci.go.kr/kciportal/ci/sereArticleSearch/ciSereArtiView.kci?sereArticleSearchBean.artiId=ART002890996</t>
+  </si>
+  <si>
+    <t>https://www.dbpia.co.kr/journal/articleDetail?nodeId=NODE11124342</t>
+  </si>
+  <si>
+    <t>https://www.dbpia.co.kr/journal/articleDetail?nodeId=NODE06586332</t>
+  </si>
+  <si>
+    <t>https://www.dbpia.co.kr/journal/articleDetail?nodeId=NODE06284662</t>
+  </si>
+  <si>
+    <t>https://www.dbpia.co.kr/journal/articleDetail?nodeId=NODE02510562</t>
+  </si>
+  <si>
+    <t>https://www.dbpia.co.kr/journal/articleDetail?nodeId=NODE06650754</t>
+  </si>
+  <si>
+    <t>https://www.dbpia.co.kr/journal/articleDetail?nodeId=NODE07272024</t>
+  </si>
+  <si>
+    <t>https://www.dbpia.co.kr/journal/articleDetail?nodeId=NODE07089398</t>
+  </si>
+  <si>
+    <t>https://www.kci.go.kr/kciportal/ci/sereArticleSearch/ciSereArtiView.kci?sereArticleSearchBean.artiId=ART002755213</t>
+  </si>
+  <si>
+    <t>https://www.kci.go.kr/kciportal/ci/sereArticleSearch/ciSereArtiView.kci?sereArticleSearchBean.artiId=ART002771970</t>
+  </si>
+  <si>
+    <t>2021, 성수연, 양재섭, 남진, 서울시 고령인구의 사회공간적 특성과 계속 거주 의향에 영향을 미치는 요인 분석_고령인구 밀집지역을 중심으로, 국토계획 56(7), 1-16.pdf</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.kci.go.kr/kciportal/ci/sereArticleSearch/ciSereArtiView.kci?sereArticleSearchBean.artiId=ART002797149</t>
+  </si>
+  <si>
+    <t>https://www.kci.go.kr/kciportal/ci/sereArticleSearch/ciSereArtiView.kci?sereArticleSearchBean.artiId=ART002751182</t>
+  </si>
+  <si>
+    <t>PUB-099와 동일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pub-096과 동일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.kci.go.kr/kciportal/ci/sereArticleSearch/ciSereArtiView.kci?sereArticleSearchBean.artiId=ART002690871</t>
+  </si>
+  <si>
+    <t>PUB-100와 동일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.kci.go.kr/kciportal/ci/sereArticleSearch/ciSereArtiView.kci?sereArticleSearchBean.artiId=ART002713517</t>
+  </si>
+  <si>
+    <t>094와동일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.kci.go.kr/kciportal/ci/sereArticleSearch/ciSereArtiView.kci?sereArticleSearchBean.artiId=ART002772071</t>
+  </si>
+  <si>
+    <t>https://www.kci.go.kr/kciportal/ci/sereArticleSearch/ciSereArtiView.kci?sereArticleSearchBean.artiId=ART002755221</t>
+  </si>
+  <si>
+    <t>https://www.kci.go.kr/kciportal/ci/sereArticleSearch/ciSereArtiView.kci?sereArticleSearchBean.artiId=ART002779765</t>
+  </si>
+  <si>
+    <t>https://www.kci.go.kr/kciportal/ci/sereArticleSearch/ciSereArtiView.kci?sereArticleSearchBean.artiId=ART002805185</t>
+  </si>
+  <si>
+    <t>https://scienceon.kisti.re.kr/srch/selectPORSrchArticle.do?cn=NART112502133</t>
+  </si>
+  <si>
+    <t>https://www.dbpia.co.kr/journal/articleDetail?nodeId=NODE09322712</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.kci.go.kr/kciportal/ci/sereArticleSearch/ciSereArtiView.kci?sereArticleSearchBean.artiId=ART002625756</t>
   </si>
 </sst>
 </file>
@@ -2232,7 +2459,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2255,6 +2482,15 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -2273,8 +2509,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2291,12 +2530,13 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="3">
     <dxf>
@@ -2785,6 +3025,9 @@
       <c r="J2" t="s">
         <v>300</v>
       </c>
+      <c r="L2" t="s">
+        <v>614</v>
+      </c>
       <c r="M2" t="s">
         <v>434</v>
       </c>
@@ -2866,6 +3109,9 @@
       <c r="I4">
         <v>4</v>
       </c>
+      <c r="L4" t="s">
+        <v>622</v>
+      </c>
       <c r="M4" t="s">
         <v>434</v>
       </c>
@@ -2908,6 +3154,9 @@
       <c r="J5" t="s">
         <v>313</v>
       </c>
+      <c r="L5" t="s">
+        <v>623</v>
+      </c>
       <c r="M5" t="s">
         <v>434</v>
       </c>
@@ -2992,6 +3241,9 @@
       <c r="J7" t="s">
         <v>310</v>
       </c>
+      <c r="L7" t="s">
+        <v>624</v>
+      </c>
       <c r="M7" t="s">
         <v>434</v>
       </c>
@@ -3025,6 +3277,9 @@
       <c r="G8" t="s">
         <v>299</v>
       </c>
+      <c r="L8" t="s">
+        <v>621</v>
+      </c>
       <c r="M8" t="s">
         <v>287</v>
       </c>
@@ -3067,6 +3322,9 @@
       <c r="J9" t="s">
         <v>317</v>
       </c>
+      <c r="L9" t="s">
+        <v>625</v>
+      </c>
       <c r="M9" t="s">
         <v>434</v>
       </c>
@@ -3094,6 +3352,9 @@
         <f>VALUE(LEFT(PublicationsTable[[#This Row],[file_name]],4))</f>
         <v>2004</v>
       </c>
+      <c r="L10" t="s">
+        <v>625</v>
+      </c>
       <c r="M10" t="s">
         <v>287</v>
       </c>
@@ -3163,6 +3424,9 @@
       <c r="I12">
         <v>6</v>
       </c>
+      <c r="L12" t="s">
+        <v>618</v>
+      </c>
       <c r="M12" t="s">
         <v>434</v>
       </c>
@@ -3199,6 +3463,9 @@
       <c r="H13">
         <v>289</v>
       </c>
+      <c r="L13" t="s">
+        <v>626</v>
+      </c>
       <c r="M13" t="s">
         <v>434</v>
       </c>
@@ -3241,6 +3508,9 @@
       <c r="J14" t="s">
         <v>324</v>
       </c>
+      <c r="L14" t="s">
+        <v>627</v>
+      </c>
       <c r="M14" t="s">
         <v>434</v>
       </c>
@@ -3307,6 +3577,9 @@
       <c r="J16" s="1" t="s">
         <v>327</v>
       </c>
+      <c r="L16" t="s">
+        <v>620</v>
+      </c>
       <c r="M16" t="s">
         <v>434</v>
       </c>
@@ -3349,6 +3622,9 @@
       <c r="J17" t="s">
         <v>335</v>
       </c>
+      <c r="L17" t="s">
+        <v>616</v>
+      </c>
       <c r="M17" t="s">
         <v>434</v>
       </c>
@@ -3391,6 +3667,9 @@
       <c r="J18" t="s">
         <v>332</v>
       </c>
+      <c r="L18" t="s">
+        <v>628</v>
+      </c>
       <c r="M18" t="s">
         <v>434</v>
       </c>
@@ -3463,6 +3742,9 @@
       <c r="J20" t="s">
         <v>330</v>
       </c>
+      <c r="L20" t="s">
+        <v>629</v>
+      </c>
       <c r="M20" t="s">
         <v>434</v>
       </c>
@@ -3505,6 +3787,9 @@
       <c r="J21" t="s">
         <v>338</v>
       </c>
+      <c r="L21" t="s">
+        <v>630</v>
+      </c>
       <c r="M21" t="s">
         <v>434</v>
       </c>
@@ -3544,6 +3829,9 @@
       <c r="I22">
         <v>7</v>
       </c>
+      <c r="L22" t="s">
+        <v>631</v>
+      </c>
       <c r="M22" t="s">
         <v>434</v>
       </c>
@@ -3583,6 +3871,9 @@
       <c r="I23">
         <v>3</v>
       </c>
+      <c r="L23" t="s">
+        <v>615</v>
+      </c>
       <c r="M23" t="s">
         <v>434</v>
       </c>
@@ -3622,6 +3913,9 @@
       <c r="I24">
         <v>3</v>
       </c>
+      <c r="L24" t="s">
+        <v>632</v>
+      </c>
       <c r="M24" t="s">
         <v>434</v>
       </c>
@@ -3958,6 +4252,9 @@
       <c r="J33" t="s">
         <v>357</v>
       </c>
+      <c r="L33" t="s">
+        <v>619</v>
+      </c>
       <c r="M33" t="s">
         <v>434</v>
       </c>
@@ -4042,6 +4339,9 @@
       <c r="J35" t="s">
         <v>367</v>
       </c>
+      <c r="L35" t="s">
+        <v>617</v>
+      </c>
       <c r="M35" t="s">
         <v>434</v>
       </c>
@@ -4786,6 +5086,9 @@
       <c r="I54">
         <v>7</v>
       </c>
+      <c r="L54" t="s">
+        <v>664</v>
+      </c>
       <c r="M54" t="s">
         <v>434</v>
       </c>
@@ -4981,6 +5284,9 @@
       <c r="I59">
         <v>3</v>
       </c>
+      <c r="L59" t="s">
+        <v>663</v>
+      </c>
       <c r="M59" t="s">
         <v>434</v>
       </c>
@@ -5020,6 +5326,9 @@
       <c r="I60">
         <v>8</v>
       </c>
+      <c r="L60" t="s">
+        <v>662</v>
+      </c>
       <c r="M60" t="s">
         <v>434</v>
       </c>
@@ -5518,6 +5827,9 @@
       <c r="I73">
         <v>1</v>
       </c>
+      <c r="L73" t="s">
+        <v>665</v>
+      </c>
       <c r="M73" t="s">
         <v>434</v>
       </c>
@@ -5557,6 +5869,9 @@
       <c r="I74">
         <v>7</v>
       </c>
+      <c r="L74" t="s">
+        <v>667</v>
+      </c>
       <c r="M74" t="s">
         <v>434</v>
       </c>
@@ -5596,6 +5911,9 @@
       <c r="I75">
         <v>6</v>
       </c>
+      <c r="L75" t="s">
+        <v>666</v>
+      </c>
       <c r="M75" t="s">
         <v>434</v>
       </c>
@@ -5804,7 +6122,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>230</v>
       </c>
@@ -5840,7 +6158,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>231</v>
       </c>
@@ -5879,7 +6197,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>232</v>
       </c>
@@ -5918,7 +6236,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>233</v>
       </c>
@@ -5957,7 +6275,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>234</v>
       </c>
@@ -5996,7 +6314,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>235</v>
       </c>
@@ -6035,7 +6353,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>236</v>
       </c>
@@ -6074,7 +6392,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>237</v>
       </c>
@@ -6113,7 +6431,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>238</v>
       </c>
@@ -6155,7 +6473,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>239</v>
       </c>
@@ -6190,6 +6508,9 @@
       <c r="M90" t="s">
         <v>434</v>
       </c>
+      <c r="N90" t="s">
+        <v>685</v>
+      </c>
       <c r="O90" t="s">
         <v>105</v>
       </c>
@@ -6197,7 +6518,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>240</v>
       </c>
@@ -6232,6 +6553,9 @@
       <c r="M91" t="s">
         <v>434</v>
       </c>
+      <c r="N91" s="4" t="s">
+        <v>684</v>
+      </c>
       <c r="O91" t="s">
         <v>106</v>
       </c>
@@ -6239,7 +6563,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>241</v>
       </c>
@@ -6271,6 +6595,9 @@
       <c r="M92" t="s">
         <v>434</v>
       </c>
+      <c r="N92" t="s">
+        <v>683</v>
+      </c>
       <c r="O92" t="s">
         <v>107</v>
       </c>
@@ -6278,7 +6605,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>242</v>
       </c>
@@ -6313,14 +6640,20 @@
       <c r="M93" t="s">
         <v>434</v>
       </c>
+      <c r="N93" t="s">
+        <v>672</v>
+      </c>
       <c r="O93" t="s">
         <v>108</v>
       </c>
       <c r="P93" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q93" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>243</v>
       </c>
@@ -6352,14 +6685,20 @@
       <c r="M94" t="s">
         <v>434</v>
       </c>
+      <c r="N94" t="s">
+        <v>675</v>
+      </c>
       <c r="O94" t="s">
         <v>493</v>
       </c>
       <c r="P94" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q94" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>244</v>
       </c>
@@ -6391,6 +6730,9 @@
       <c r="M95" t="s">
         <v>434</v>
       </c>
+      <c r="N95" t="s">
+        <v>677</v>
+      </c>
       <c r="O95" t="s">
         <v>495</v>
       </c>
@@ -6398,7 +6740,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>245</v>
       </c>
@@ -6427,8 +6769,14 @@
       <c r="I96">
         <v>7</v>
       </c>
+      <c r="J96" s="3" t="s">
+        <v>502</v>
+      </c>
       <c r="M96" t="s">
         <v>434</v>
+      </c>
+      <c r="N96" t="s">
+        <v>671</v>
       </c>
       <c r="O96" t="s">
         <v>497</v>
@@ -6436,8 +6784,11 @@
       <c r="P96" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q96" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>246</v>
       </c>
@@ -6470,7 +6821,7 @@
         <v>502</v>
       </c>
       <c r="M97" t="s">
-        <v>434</v>
+        <v>287</v>
       </c>
       <c r="O97" t="s">
         <v>112</v>
@@ -6479,7 +6830,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>247</v>
       </c>
@@ -6514,6 +6865,9 @@
       <c r="M98" t="s">
         <v>434</v>
       </c>
+      <c r="N98" t="s">
+        <v>668</v>
+      </c>
       <c r="O98" t="s">
         <v>113</v>
       </c>
@@ -6521,7 +6875,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>248</v>
       </c>
@@ -6556,6 +6910,9 @@
       <c r="M99" t="s">
         <v>434</v>
       </c>
+      <c r="N99" t="s">
+        <v>669</v>
+      </c>
       <c r="O99" t="s">
         <v>114</v>
       </c>
@@ -6563,7 +6920,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>249</v>
       </c>
@@ -6596,16 +6953,16 @@
         <v>502</v>
       </c>
       <c r="M100" t="s">
-        <v>434</v>
+        <v>287</v>
       </c>
       <c r="O100" t="s">
-        <v>115</v>
+        <v>670</v>
       </c>
       <c r="P100" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>250</v>
       </c>
@@ -6638,7 +6995,7 @@
         <v>512</v>
       </c>
       <c r="M101" t="s">
-        <v>434</v>
+        <v>287</v>
       </c>
       <c r="O101" t="s">
         <v>116</v>
@@ -6647,7 +7004,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>251</v>
       </c>
@@ -6682,6 +7039,9 @@
       <c r="M102" t="s">
         <v>434</v>
       </c>
+      <c r="N102" t="s">
+        <v>682</v>
+      </c>
       <c r="O102" t="s">
         <v>117</v>
       </c>
@@ -6689,7 +7049,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>252</v>
       </c>
@@ -6722,7 +7082,7 @@
         <v>512</v>
       </c>
       <c r="M103" t="s">
-        <v>434</v>
+        <v>287</v>
       </c>
       <c r="O103" t="s">
         <v>118</v>
@@ -6730,8 +7090,11 @@
       <c r="P103" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q103" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>253</v>
       </c>
@@ -6766,6 +7129,9 @@
       <c r="M104" t="s">
         <v>434</v>
       </c>
+      <c r="N104" t="s">
+        <v>681</v>
+      </c>
       <c r="O104" t="s">
         <v>119</v>
       </c>
@@ -6773,7 +7139,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>254</v>
       </c>
@@ -6808,6 +7174,9 @@
       <c r="M105" t="s">
         <v>434</v>
       </c>
+      <c r="N105" t="s">
+        <v>679</v>
+      </c>
       <c r="O105" t="s">
         <v>120</v>
       </c>
@@ -6815,7 +7184,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>255</v>
       </c>
@@ -6850,6 +7219,9 @@
       <c r="M106" t="s">
         <v>434</v>
       </c>
+      <c r="N106" t="s">
+        <v>680</v>
+      </c>
       <c r="O106" t="s">
         <v>121</v>
       </c>
@@ -6857,7 +7229,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>256</v>
       </c>
@@ -6889,6 +7261,9 @@
       <c r="M107" t="s">
         <v>434</v>
       </c>
+      <c r="N107" t="s">
+        <v>661</v>
+      </c>
       <c r="O107" t="s">
         <v>122</v>
       </c>
@@ -6896,7 +7271,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>257</v>
       </c>
@@ -6931,6 +7306,9 @@
       <c r="M108" t="s">
         <v>434</v>
       </c>
+      <c r="N108" t="s">
+        <v>660</v>
+      </c>
       <c r="O108" t="s">
         <v>123</v>
       </c>
@@ -6938,7 +7316,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>258</v>
       </c>
@@ -6973,6 +7351,9 @@
       <c r="M109" t="s">
         <v>434</v>
       </c>
+      <c r="N109" t="s">
+        <v>659</v>
+      </c>
       <c r="O109" t="s">
         <v>124</v>
       </c>
@@ -6980,7 +7361,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>259</v>
       </c>
@@ -7012,6 +7393,9 @@
       <c r="M110" t="s">
         <v>434</v>
       </c>
+      <c r="N110" s="4" t="s">
+        <v>658</v>
+      </c>
       <c r="O110" t="s">
         <v>125</v>
       </c>
@@ -7019,7 +7403,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>260</v>
       </c>
@@ -7051,6 +7435,9 @@
       <c r="M111" t="s">
         <v>434</v>
       </c>
+      <c r="N111" s="4" t="s">
+        <v>657</v>
+      </c>
       <c r="O111" t="s">
         <v>126</v>
       </c>
@@ -7058,7 +7445,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>261</v>
       </c>
@@ -7092,6 +7479,9 @@
       </c>
       <c r="M112" t="s">
         <v>434</v>
+      </c>
+      <c r="N112" t="s">
+        <v>656</v>
       </c>
       <c r="O112" t="s">
         <v>127</v>
@@ -7135,6 +7525,9 @@
       <c r="M113" t="s">
         <v>434</v>
       </c>
+      <c r="N113" t="s">
+        <v>655</v>
+      </c>
       <c r="O113" t="s">
         <v>128</v>
       </c>
@@ -7177,6 +7570,9 @@
       <c r="M114" t="s">
         <v>434</v>
       </c>
+      <c r="N114" t="s">
+        <v>654</v>
+      </c>
       <c r="O114" t="s">
         <v>129</v>
       </c>
@@ -7216,6 +7612,9 @@
       <c r="M115" t="s">
         <v>434</v>
       </c>
+      <c r="N115" t="s">
+        <v>653</v>
+      </c>
       <c r="O115" t="s">
         <v>130</v>
       </c>
@@ -7255,6 +7654,9 @@
       <c r="M116" t="s">
         <v>434</v>
       </c>
+      <c r="N116" t="s">
+        <v>652</v>
+      </c>
       <c r="O116" t="s">
         <v>131</v>
       </c>
@@ -7297,6 +7699,9 @@
       <c r="M117" t="s">
         <v>434</v>
       </c>
+      <c r="N117" t="s">
+        <v>651</v>
+      </c>
       <c r="O117" t="s">
         <v>132</v>
       </c>
@@ -7339,6 +7744,9 @@
       <c r="M118" t="s">
         <v>434</v>
       </c>
+      <c r="N118" t="s">
+        <v>650</v>
+      </c>
       <c r="O118" t="s">
         <v>133</v>
       </c>
@@ -7381,6 +7789,9 @@
       <c r="M119" t="s">
         <v>434</v>
       </c>
+      <c r="N119" t="s">
+        <v>649</v>
+      </c>
       <c r="O119" t="s">
         <v>134</v>
       </c>
@@ -7423,6 +7834,9 @@
       <c r="M120" t="s">
         <v>434</v>
       </c>
+      <c r="N120" t="s">
+        <v>648</v>
+      </c>
       <c r="O120" t="s">
         <v>135</v>
       </c>
@@ -7465,6 +7879,9 @@
       <c r="M121" t="s">
         <v>434</v>
       </c>
+      <c r="N121" t="s">
+        <v>647</v>
+      </c>
       <c r="O121" t="s">
         <v>136</v>
       </c>
@@ -7507,6 +7924,9 @@
       <c r="M122" t="s">
         <v>434</v>
       </c>
+      <c r="N122" s="4" t="s">
+        <v>646</v>
+      </c>
       <c r="O122" t="s">
         <v>137</v>
       </c>
@@ -7549,6 +7969,9 @@
       <c r="M123" t="s">
         <v>434</v>
       </c>
+      <c r="N123" t="s">
+        <v>645</v>
+      </c>
       <c r="O123" t="s">
         <v>138</v>
       </c>
@@ -7591,6 +8014,9 @@
       <c r="M124" t="s">
         <v>434</v>
       </c>
+      <c r="N124" s="4" t="s">
+        <v>644</v>
+      </c>
       <c r="O124" t="s">
         <v>139</v>
       </c>
@@ -7633,6 +8059,9 @@
       <c r="M125" t="s">
         <v>434</v>
       </c>
+      <c r="N125" t="s">
+        <v>643</v>
+      </c>
       <c r="O125" t="s">
         <v>140</v>
       </c>
@@ -7669,6 +8098,9 @@
       <c r="M126" t="s">
         <v>434</v>
       </c>
+      <c r="N126" t="s">
+        <v>642</v>
+      </c>
       <c r="O126" t="s">
         <v>141</v>
       </c>
@@ -7711,6 +8143,9 @@
       <c r="M127" t="s">
         <v>434</v>
       </c>
+      <c r="N127" t="s">
+        <v>641</v>
+      </c>
       <c r="O127" t="s">
         <v>142</v>
       </c>
@@ -7753,6 +8188,9 @@
       <c r="M128" t="s">
         <v>434</v>
       </c>
+      <c r="N128" t="s">
+        <v>640</v>
+      </c>
       <c r="O128" t="s">
         <v>143</v>
       </c>
@@ -7798,6 +8236,9 @@
       <c r="M129" t="s">
         <v>434</v>
       </c>
+      <c r="N129" t="s">
+        <v>639</v>
+      </c>
       <c r="O129" t="s">
         <v>144</v>
       </c>
@@ -7840,6 +8281,9 @@
       <c r="M130" t="s">
         <v>434</v>
       </c>
+      <c r="N130" s="4" t="s">
+        <v>638</v>
+      </c>
       <c r="O130" t="s">
         <v>145</v>
       </c>
@@ -7882,6 +8326,9 @@
       <c r="M131" t="s">
         <v>434</v>
       </c>
+      <c r="N131" t="s">
+        <v>637</v>
+      </c>
       <c r="O131" t="s">
         <v>146</v>
       </c>
@@ -7921,6 +8368,9 @@
       <c r="M132" t="s">
         <v>434</v>
       </c>
+      <c r="N132" t="s">
+        <v>636</v>
+      </c>
       <c r="O132" t="s">
         <v>147</v>
       </c>
@@ -7963,6 +8413,9 @@
       <c r="M133" t="s">
         <v>434</v>
       </c>
+      <c r="N133" t="s">
+        <v>635</v>
+      </c>
       <c r="O133" t="s">
         <v>148</v>
       </c>
@@ -8005,6 +8458,9 @@
       <c r="M134" t="s">
         <v>434</v>
       </c>
+      <c r="N134" t="s">
+        <v>634</v>
+      </c>
       <c r="O134" t="s">
         <v>149</v>
       </c>
@@ -8047,6 +8503,9 @@
       <c r="M135" t="s">
         <v>434</v>
       </c>
+      <c r="N135" t="s">
+        <v>633</v>
+      </c>
       <c r="O135" t="s">
         <v>150</v>
       </c>
@@ -8089,7 +8548,7 @@
       <c r="M136" t="s">
         <v>434</v>
       </c>
-      <c r="O136" s="4" t="s">
+      <c r="O136" t="s">
         <v>608</v>
       </c>
       <c r="P136" t="s">
@@ -8131,7 +8590,7 @@
       <c r="M137" t="s">
         <v>434</v>
       </c>
-      <c r="O137" s="4" t="s">
+      <c r="O137" t="s">
         <v>613</v>
       </c>
       <c r="P137" t="s">
@@ -8151,9 +8610,17 @@
       <formula1>"Y,N"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="N130" r:id="rId1" xr:uid="{3B221264-9B57-4EFB-A972-E50C843488C9}"/>
+    <hyperlink ref="N124" r:id="rId2" xr:uid="{17A48322-5B7C-4290-8601-48F6E538CA51}"/>
+    <hyperlink ref="N122" r:id="rId3" xr:uid="{8E9391E4-744E-4AD3-8793-B60E6BE661B9}"/>
+    <hyperlink ref="N111" r:id="rId4" xr:uid="{0D92085D-1513-44F0-87F5-537487506C7C}"/>
+    <hyperlink ref="N110" r:id="rId5" xr:uid="{A485EFB8-2A9F-4776-B137-EE6FCC49F5CA}"/>
+    <hyperlink ref="N91" r:id="rId6" xr:uid="{EEAE9123-2018-46E9-B02E-EE5C09052273}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId7"/>
   </tableParts>
 </worksheet>
 </file>

--- a/data/publications.xlsx
+++ b/data/publications.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SmartCity20\.gemini\antigravity\scratch\surd-lab-homepage\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B00B015-CD3E-42A6-8685-316E8652F85A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3AF748C-7FFC-441F-B98D-B6A1871729F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25800" yWindow="0" windowWidth="25800" windowHeight="21000" xr2:uid="{FB3B5A28-B30A-4FB9-B973-DA7691D44842}"/>
+    <workbookView xWindow="6570" yWindow="3825" windowWidth="38700" windowHeight="15435" xr2:uid="{FB3B5A28-B30A-4FB9-B973-DA7691D44842}"/>
   </bookViews>
   <sheets>
     <sheet name="publications" sheetId="1" r:id="rId1"/>
@@ -6505,11 +6505,11 @@
       <c r="J90" t="s">
         <v>483</v>
       </c>
+      <c r="L90" t="s">
+        <v>685</v>
+      </c>
       <c r="M90" t="s">
         <v>434</v>
-      </c>
-      <c r="N90" t="s">
-        <v>685</v>
       </c>
       <c r="O90" t="s">
         <v>105</v>
@@ -6550,11 +6550,11 @@
       <c r="J91" t="s">
         <v>486</v>
       </c>
+      <c r="L91" s="4" t="s">
+        <v>684</v>
+      </c>
       <c r="M91" t="s">
         <v>434</v>
-      </c>
-      <c r="N91" s="4" t="s">
-        <v>684</v>
       </c>
       <c r="O91" t="s">
         <v>106</v>
@@ -6592,11 +6592,11 @@
       <c r="I92">
         <v>2</v>
       </c>
+      <c r="L92" t="s">
+        <v>683</v>
+      </c>
       <c r="M92" t="s">
         <v>434</v>
-      </c>
-      <c r="N92" t="s">
-        <v>683</v>
       </c>
       <c r="O92" t="s">
         <v>107</v>
@@ -6637,11 +6637,11 @@
       <c r="J93" t="s">
         <v>492</v>
       </c>
+      <c r="L93" t="s">
+        <v>672</v>
+      </c>
       <c r="M93" t="s">
         <v>434</v>
-      </c>
-      <c r="N93" t="s">
-        <v>672</v>
       </c>
       <c r="O93" t="s">
         <v>108</v>
@@ -6682,11 +6682,11 @@
       <c r="I94">
         <v>1</v>
       </c>
+      <c r="L94" t="s">
+        <v>675</v>
+      </c>
       <c r="M94" t="s">
         <v>434</v>
-      </c>
-      <c r="N94" t="s">
-        <v>675</v>
       </c>
       <c r="O94" t="s">
         <v>493</v>
@@ -6727,11 +6727,11 @@
       <c r="I95">
         <v>1</v>
       </c>
+      <c r="L95" t="s">
+        <v>677</v>
+      </c>
       <c r="M95" t="s">
         <v>434</v>
-      </c>
-      <c r="N95" t="s">
-        <v>677</v>
       </c>
       <c r="O95" t="s">
         <v>495</v>
@@ -6772,11 +6772,11 @@
       <c r="J96" s="3" t="s">
         <v>502</v>
       </c>
+      <c r="L96" t="s">
+        <v>671</v>
+      </c>
       <c r="M96" t="s">
         <v>434</v>
-      </c>
-      <c r="N96" t="s">
-        <v>671</v>
       </c>
       <c r="O96" t="s">
         <v>497</v>
@@ -6862,11 +6862,11 @@
       <c r="J98" t="s">
         <v>505</v>
       </c>
+      <c r="L98" t="s">
+        <v>668</v>
+      </c>
       <c r="M98" t="s">
         <v>434</v>
-      </c>
-      <c r="N98" t="s">
-        <v>668</v>
       </c>
       <c r="O98" t="s">
         <v>113</v>
@@ -6907,11 +6907,11 @@
       <c r="J99" s="3" t="s">
         <v>507</v>
       </c>
+      <c r="L99" t="s">
+        <v>669</v>
+      </c>
       <c r="M99" t="s">
         <v>434</v>
-      </c>
-      <c r="N99" t="s">
-        <v>669</v>
       </c>
       <c r="O99" t="s">
         <v>114</v>
@@ -7036,11 +7036,11 @@
       <c r="J102" t="s">
         <v>515</v>
       </c>
+      <c r="L102" t="s">
+        <v>682</v>
+      </c>
       <c r="M102" t="s">
         <v>434</v>
-      </c>
-      <c r="N102" t="s">
-        <v>682</v>
       </c>
       <c r="O102" t="s">
         <v>117</v>
@@ -7126,11 +7126,11 @@
       <c r="J104" t="s">
         <v>522</v>
       </c>
+      <c r="L104" t="s">
+        <v>681</v>
+      </c>
       <c r="M104" t="s">
         <v>434</v>
-      </c>
-      <c r="N104" t="s">
-        <v>681</v>
       </c>
       <c r="O104" t="s">
         <v>119</v>
@@ -7171,11 +7171,11 @@
       <c r="J105" t="s">
         <v>520</v>
       </c>
+      <c r="L105" t="s">
+        <v>679</v>
+      </c>
       <c r="M105" t="s">
         <v>434</v>
-      </c>
-      <c r="N105" t="s">
-        <v>679</v>
       </c>
       <c r="O105" t="s">
         <v>120</v>
@@ -7216,11 +7216,11 @@
       <c r="J106" t="s">
         <v>525</v>
       </c>
+      <c r="L106" t="s">
+        <v>680</v>
+      </c>
       <c r="M106" t="s">
         <v>434</v>
-      </c>
-      <c r="N106" t="s">
-        <v>680</v>
       </c>
       <c r="O106" t="s">
         <v>121</v>
@@ -7258,11 +7258,11 @@
       <c r="I107">
         <v>4</v>
       </c>
+      <c r="L107" t="s">
+        <v>661</v>
+      </c>
       <c r="M107" t="s">
         <v>434</v>
-      </c>
-      <c r="N107" t="s">
-        <v>661</v>
       </c>
       <c r="O107" t="s">
         <v>122</v>
@@ -7303,11 +7303,11 @@
       <c r="J108" t="s">
         <v>530</v>
       </c>
+      <c r="L108" t="s">
+        <v>660</v>
+      </c>
       <c r="M108" t="s">
         <v>434</v>
-      </c>
-      <c r="N108" t="s">
-        <v>660</v>
       </c>
       <c r="O108" t="s">
         <v>123</v>
@@ -7348,11 +7348,11 @@
       <c r="J109" t="s">
         <v>534</v>
       </c>
+      <c r="L109" t="s">
+        <v>659</v>
+      </c>
       <c r="M109" t="s">
         <v>434</v>
-      </c>
-      <c r="N109" t="s">
-        <v>659</v>
       </c>
       <c r="O109" t="s">
         <v>124</v>
@@ -7390,11 +7390,11 @@
       <c r="I110">
         <v>4</v>
       </c>
+      <c r="L110" s="4" t="s">
+        <v>658</v>
+      </c>
       <c r="M110" t="s">
         <v>434</v>
-      </c>
-      <c r="N110" s="4" t="s">
-        <v>658</v>
       </c>
       <c r="O110" t="s">
         <v>125</v>
@@ -7432,11 +7432,11 @@
       <c r="I111">
         <v>1</v>
       </c>
+      <c r="L111" s="4" t="s">
+        <v>657</v>
+      </c>
       <c r="M111" t="s">
         <v>434</v>
-      </c>
-      <c r="N111" s="4" t="s">
-        <v>657</v>
       </c>
       <c r="O111" t="s">
         <v>126</v>
@@ -7477,11 +7477,11 @@
       <c r="J112" t="s">
         <v>541</v>
       </c>
+      <c r="L112" t="s">
+        <v>656</v>
+      </c>
       <c r="M112" t="s">
         <v>434</v>
-      </c>
-      <c r="N112" t="s">
-        <v>656</v>
       </c>
       <c r="O112" t="s">
         <v>127</v>
@@ -7522,11 +7522,11 @@
       <c r="J113" t="s">
         <v>543</v>
       </c>
+      <c r="L113" t="s">
+        <v>655</v>
+      </c>
       <c r="M113" t="s">
         <v>434</v>
-      </c>
-      <c r="N113" t="s">
-        <v>655</v>
       </c>
       <c r="O113" t="s">
         <v>128</v>
@@ -7567,11 +7567,11 @@
       <c r="J114" t="s">
         <v>546</v>
       </c>
+      <c r="L114" t="s">
+        <v>654</v>
+      </c>
       <c r="M114" t="s">
         <v>434</v>
-      </c>
-      <c r="N114" t="s">
-        <v>654</v>
       </c>
       <c r="O114" t="s">
         <v>129</v>
@@ -7609,11 +7609,11 @@
       <c r="I115">
         <v>3</v>
       </c>
+      <c r="L115" t="s">
+        <v>653</v>
+      </c>
       <c r="M115" t="s">
         <v>434</v>
-      </c>
-      <c r="N115" t="s">
-        <v>653</v>
       </c>
       <c r="O115" t="s">
         <v>130</v>
@@ -7651,11 +7651,11 @@
       <c r="I116">
         <v>1</v>
       </c>
+      <c r="L116" t="s">
+        <v>652</v>
+      </c>
       <c r="M116" t="s">
         <v>434</v>
-      </c>
-      <c r="N116" t="s">
-        <v>652</v>
       </c>
       <c r="O116" t="s">
         <v>131</v>
@@ -7696,11 +7696,11 @@
       <c r="J117" t="s">
         <v>550</v>
       </c>
+      <c r="L117" t="s">
+        <v>651</v>
+      </c>
       <c r="M117" t="s">
         <v>434</v>
-      </c>
-      <c r="N117" t="s">
-        <v>651</v>
       </c>
       <c r="O117" t="s">
         <v>132</v>
@@ -7741,11 +7741,11 @@
       <c r="J118" t="s">
         <v>553</v>
       </c>
+      <c r="L118" t="s">
+        <v>650</v>
+      </c>
       <c r="M118" t="s">
         <v>434</v>
-      </c>
-      <c r="N118" t="s">
-        <v>650</v>
       </c>
       <c r="O118" t="s">
         <v>133</v>
@@ -7786,11 +7786,11 @@
       <c r="J119" t="s">
         <v>556</v>
       </c>
+      <c r="L119" t="s">
+        <v>649</v>
+      </c>
       <c r="M119" t="s">
         <v>434</v>
-      </c>
-      <c r="N119" t="s">
-        <v>649</v>
       </c>
       <c r="O119" t="s">
         <v>134</v>
@@ -7831,11 +7831,11 @@
       <c r="J120" t="s">
         <v>560</v>
       </c>
+      <c r="L120" t="s">
+        <v>648</v>
+      </c>
       <c r="M120" t="s">
         <v>434</v>
-      </c>
-      <c r="N120" t="s">
-        <v>648</v>
       </c>
       <c r="O120" t="s">
         <v>135</v>
@@ -7876,11 +7876,11 @@
       <c r="J121" t="s">
         <v>563</v>
       </c>
+      <c r="L121" t="s">
+        <v>647</v>
+      </c>
       <c r="M121" t="s">
         <v>434</v>
-      </c>
-      <c r="N121" t="s">
-        <v>647</v>
       </c>
       <c r="O121" t="s">
         <v>136</v>
@@ -7921,11 +7921,11 @@
       <c r="J122" t="s">
         <v>565</v>
       </c>
+      <c r="L122" s="4" t="s">
+        <v>646</v>
+      </c>
       <c r="M122" t="s">
         <v>434</v>
-      </c>
-      <c r="N122" s="4" t="s">
-        <v>646</v>
       </c>
       <c r="O122" t="s">
         <v>137</v>
@@ -7966,11 +7966,11 @@
       <c r="J123" t="s">
         <v>568</v>
       </c>
+      <c r="L123" t="s">
+        <v>645</v>
+      </c>
       <c r="M123" t="s">
         <v>434</v>
-      </c>
-      <c r="N123" t="s">
-        <v>645</v>
       </c>
       <c r="O123" t="s">
         <v>138</v>
@@ -8011,11 +8011,11 @@
       <c r="J124" t="s">
         <v>571</v>
       </c>
+      <c r="L124" s="4" t="s">
+        <v>644</v>
+      </c>
       <c r="M124" t="s">
         <v>434</v>
-      </c>
-      <c r="N124" s="4" t="s">
-        <v>644</v>
       </c>
       <c r="O124" t="s">
         <v>139</v>
@@ -8056,11 +8056,11 @@
       <c r="J125" t="s">
         <v>574</v>
       </c>
+      <c r="L125" t="s">
+        <v>643</v>
+      </c>
       <c r="M125" t="s">
         <v>434</v>
-      </c>
-      <c r="N125" t="s">
-        <v>643</v>
       </c>
       <c r="O125" t="s">
         <v>140</v>
@@ -8095,11 +8095,11 @@
       <c r="H126">
         <v>150</v>
       </c>
+      <c r="L126" t="s">
+        <v>642</v>
+      </c>
       <c r="M126" t="s">
         <v>434</v>
-      </c>
-      <c r="N126" t="s">
-        <v>642</v>
       </c>
       <c r="O126" t="s">
         <v>141</v>
@@ -8140,11 +8140,11 @@
       <c r="J127" t="s">
         <v>579</v>
       </c>
+      <c r="L127" t="s">
+        <v>641</v>
+      </c>
       <c r="M127" t="s">
         <v>434</v>
-      </c>
-      <c r="N127" t="s">
-        <v>641</v>
       </c>
       <c r="O127" t="s">
         <v>142</v>
@@ -8185,11 +8185,11 @@
       <c r="I128">
         <v>6</v>
       </c>
+      <c r="L128" t="s">
+        <v>640</v>
+      </c>
       <c r="M128" t="s">
         <v>434</v>
-      </c>
-      <c r="N128" t="s">
-        <v>640</v>
       </c>
       <c r="O128" t="s">
         <v>143</v>
@@ -8233,11 +8233,11 @@
       <c r="J129" s="3" t="s">
         <v>583</v>
       </c>
+      <c r="L129" t="s">
+        <v>639</v>
+      </c>
       <c r="M129" t="s">
         <v>434</v>
-      </c>
-      <c r="N129" t="s">
-        <v>639</v>
       </c>
       <c r="O129" t="s">
         <v>144</v>
@@ -8278,11 +8278,11 @@
       <c r="J130" t="s">
         <v>586</v>
       </c>
+      <c r="L130" s="4" t="s">
+        <v>638</v>
+      </c>
       <c r="M130" t="s">
         <v>434</v>
-      </c>
-      <c r="N130" s="4" t="s">
-        <v>638</v>
       </c>
       <c r="O130" t="s">
         <v>145</v>
@@ -8323,11 +8323,11 @@
       <c r="J131" t="s">
         <v>486</v>
       </c>
+      <c r="L131" t="s">
+        <v>637</v>
+      </c>
       <c r="M131" t="s">
         <v>434</v>
-      </c>
-      <c r="N131" t="s">
-        <v>637</v>
       </c>
       <c r="O131" t="s">
         <v>146</v>
@@ -8365,11 +8365,11 @@
       <c r="J132" t="s">
         <v>592</v>
       </c>
+      <c r="L132" t="s">
+        <v>636</v>
+      </c>
       <c r="M132" t="s">
         <v>434</v>
-      </c>
-      <c r="N132" t="s">
-        <v>636</v>
       </c>
       <c r="O132" t="s">
         <v>147</v>
@@ -8410,11 +8410,11 @@
       <c r="J133" t="s">
         <v>594</v>
       </c>
+      <c r="L133" t="s">
+        <v>635</v>
+      </c>
       <c r="M133" t="s">
         <v>434</v>
-      </c>
-      <c r="N133" t="s">
-        <v>635</v>
       </c>
       <c r="O133" t="s">
         <v>148</v>
@@ -8455,11 +8455,11 @@
       <c r="J134" t="s">
         <v>597</v>
       </c>
+      <c r="L134" t="s">
+        <v>634</v>
+      </c>
       <c r="M134" t="s">
         <v>434</v>
-      </c>
-      <c r="N134" t="s">
-        <v>634</v>
       </c>
       <c r="O134" t="s">
         <v>149</v>
@@ -8500,11 +8500,11 @@
       <c r="J135" s="1" t="s">
         <v>599</v>
       </c>
+      <c r="L135" t="s">
+        <v>633</v>
+      </c>
       <c r="M135" t="s">
         <v>434</v>
-      </c>
-      <c r="N135" t="s">
-        <v>633</v>
       </c>
       <c r="O135" t="s">
         <v>150</v>
@@ -8611,12 +8611,12 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="N130" r:id="rId1" xr:uid="{3B221264-9B57-4EFB-A972-E50C843488C9}"/>
-    <hyperlink ref="N124" r:id="rId2" xr:uid="{17A48322-5B7C-4290-8601-48F6E538CA51}"/>
-    <hyperlink ref="N122" r:id="rId3" xr:uid="{8E9391E4-744E-4AD3-8793-B60E6BE661B9}"/>
-    <hyperlink ref="N111" r:id="rId4" xr:uid="{0D92085D-1513-44F0-87F5-537487506C7C}"/>
-    <hyperlink ref="N110" r:id="rId5" xr:uid="{A485EFB8-2A9F-4776-B137-EE6FCC49F5CA}"/>
-    <hyperlink ref="N91" r:id="rId6" xr:uid="{EEAE9123-2018-46E9-B02E-EE5C09052273}"/>
+    <hyperlink ref="L130" r:id="rId1" xr:uid="{3B221264-9B57-4EFB-A972-E50C843488C9}"/>
+    <hyperlink ref="L124" r:id="rId2" xr:uid="{17A48322-5B7C-4290-8601-48F6E538CA51}"/>
+    <hyperlink ref="L122" r:id="rId3" xr:uid="{8E9391E4-744E-4AD3-8793-B60E6BE661B9}"/>
+    <hyperlink ref="L111" r:id="rId4" xr:uid="{0D92085D-1513-44F0-87F5-537487506C7C}"/>
+    <hyperlink ref="L110" r:id="rId5" xr:uid="{A485EFB8-2A9F-4776-B137-EE6FCC49F5CA}"/>
+    <hyperlink ref="L91" r:id="rId6" xr:uid="{EEAE9123-2018-46E9-B02E-EE5C09052273}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
